--- a/Red_Bull_failed_to_download.xlsx
+++ b/Red_Bull_failed_to_download.xlsx
@@ -437,12 +437,12 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15281468784</v>
+        <v>15280955623</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15280955623</v>
+        <v>15281468784</v>
       </c>
     </row>
   </sheetData>
